--- a/output/2026年2月党费收缴明细表.xlsx
+++ b/output/2026年2月党费收缴明细表.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,13 +110,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -622,7 +623,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>教工第一支部</t>
+          <t>研究生第一党支部</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -630,50 +631,50 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>车树鹏</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2185</v>
+        <v>4640</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1100</v>
+        <v>2590</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1094</v>
+        <v>2225</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>152.62</v>
+        <v>321.62</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>706.72</v>
+        <v>1454.96</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>353.36</v>
+        <v>727.48</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>39.66</v>
+        <v>80.41</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>44.17</v>
+        <v>90.94</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>37.06</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>1586.47</v>
+        <v>2514.530000000001</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>7.9</v>
+        <v>12.6</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>20.6</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5">
@@ -684,65 +685,59 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>孙世纪</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2375</v>
+        <v>0.2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>845</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2030</v>
+        <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>165.78</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>785.62</v>
+        <v>0</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>392.81</v>
+        <v>0</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>45.32</v>
+        <v>0</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>52.43</v>
+        <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>67.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>2540.47</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="R5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>本科生第一支部</t>
-        </is>
-      </c>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -784,73 +779,16 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6" t="n"/>
+      <c r="R6" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="R4:R6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/2026年2月党费收缴明细表.xlsx
+++ b/output/2026年2月党费收缴明细表.xlsx
@@ -54,7 +54,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,32 +68,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,14 +89,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -631,164 +602,60 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>车树鹏</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4640</v>
+        <v>0.2</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2590</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>321.62</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1454.96</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>727.48</v>
+        <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>80.41</v>
+        <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>90.94</v>
+        <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>37.06</v>
+        <v>0</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>2514.530000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>孙世纪</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9" t="n"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="R4:R6"/>
+    <mergeCell ref="A4"/>
+    <mergeCell ref="B4"/>
+    <mergeCell ref="R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
